--- a/daily_matches/job_matches_2026-08-31.xlsx
+++ b/daily_matches/job_matches_2026-08-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIPowered Power BI Engineer</t>
+          <t>Software Developer Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Dataflow, Snowflake, Power BI, Python, SQL</t>
+          <t>LangChain, LLaMA, Copilot, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5865f55ab1e5c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=be58d44ac5525421</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technical Implementation Consultant</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,112 +531,882 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0ad4cd05769a68</t>
+          <t>https://www.indeed.com/viewjob?jk=8aab1ba56e62f502</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer/Software Engineer III (Data Engineering)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Kafka, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3dc3ae389abf7c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fad893368beea94</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern (E-Commerce Knowledge Graph) - 2027 Start (PhD)</t>
+          <t>Analytics Forward Deployed Software Engineer 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Tampa General Hospital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Hadoop, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Prompt Engineering, Data Lake, Git, PySpark, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d64bee1175c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c9283ca95a99612</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern (E-Commerce Knowledge Graph) - 2027 Start (PhD)</t>
+          <t>Senior Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8c0b2d123347de</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TopDog Law</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Glue, BigQuery, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e1157771c4bef2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sr. AI/ML Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8b464b84f6efe85</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior AI-Native Forward Deployed Engineer | Remote | Long Term | C2C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tms Llc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40f998c31712a890</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior CyberTech Engineer (Specialist - Data Sciences)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Athena, BigQuery, Data Lake, Snowflake, BigQuery, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6f7fb2607b06cd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site Reliable Engineer (US - Remote)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Axon Networks</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=507ad84b2def3781</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TransUnion</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0f1d17f751a189</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Redshift, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rakuten Global</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83a8fd93c615f865</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Decatur, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Qorvo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bend, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>11.1</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Hadoop, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca4286f9428cb0b</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b57fe7a9db67650</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AWS Data &amp; AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50ebd00f72efef21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Infrastructure Engineer - NREC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Docker, AKS, CI/CD, Jenkins, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15f3944be5390d23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineering, Sr Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Synopsys</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7c27d39498fc808</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Git, Redshift, PostgreSQL, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ai Development Specialist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a4bfc6dc3f97709</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Technical Customer Support Engineer, AI Infrastructure &amp; Observability - EMEA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Kinesis, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccf74bbdaa26d105</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lions Path Consulting</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Franklin, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01033f717bc9cb90</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Fintech</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=055e12468c2b025b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f4ead9aa90b5f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Systems &amp; Network Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Docker, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37d8c5222063ca0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AQR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Greenwich, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, S3, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cfb20f3e398d595</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mitti Cafe</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23ae46ccdee20ba1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-31.xlsx
+++ b/daily_matches/job_matches_2026-08-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Developer Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Copilot, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be58d44ac5525421</t>
+          <t>https://www.indeed.com/viewjob?jk=dbf686b10c85ee8a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Xactus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Broomall, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, Glue, MLflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aab1ba56e62f502</t>
+          <t>https://www.indeed.com/viewjob?jk=dec641935aaf0ea6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI Engineer / Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Egrove Systems Pvt.Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fad893368beea94</t>
+          <t>https://www.indeed.com/viewjob?jk=437bdfcae26b8ec0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Forward Deployed Software Engineer 2</t>
+          <t>Cloud Vulnerability Management Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tampa General Hospital</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, Data Lake, Git, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c9283ca95a99612</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence/Machine Learning Engineer</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Forman Technology Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8c0b2d123347de</t>
+          <t>https://www.indeed.com/viewjob?jk=88845cae349f7c04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure AI Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TopDog Law</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Glue, BigQuery, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1157771c4bef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Remote</t>
+          <t>Engineer II, AI/ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MongoDB, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b464b84f6efe85</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8e6dec72952725</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI-Native Forward Deployed Engineer | Remote | Long Term | C2C</t>
+          <t>Engineer II, AI/ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40f998c31712a890</t>
+          <t>https://www.indeed.com/viewjob?jk=3e91b8f820103b48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior CyberTech Engineer (Specialist - Data Sciences)</t>
+          <t>AI / LLM Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Sierra Nevada Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lone Tree, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, BigQuery, Data Lake, Snowflake, BigQuery, Python, R, Scala</t>
+          <t>Generative AI, LangChain, LLaMA, Mistral, Prompt Engineering, MLflow, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f7fb2607b06cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=4dc1b8c70f708361</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliable Engineer (US - Remote)</t>
+          <t>Engineer II - Software Development (Python / AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Jenkins, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507ad84b2def3781</t>
+          <t>https://www.indeed.com/viewjob?jk=25656ef8eb28ff16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Security Automation Engineer</t>
+          <t>Senior Data Analyst - Clinican Experience</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TransUnion</t>
+          <t>Midi Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Cortex, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Athena, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0f1d17f751a189</t>
+          <t>https://www.indeed.com/viewjob?jk=286660e90a48fbb4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Redshift, MySQL, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>Technology Consultant - Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a8fd93c615f865</t>
+          <t>https://www.indeed.com/viewjob?jk=aff7320f2676a7bb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advanced Forward Engineering - Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Decatur, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, AKS, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
+          <t>https://www.indeed.com/viewjob?jk=deea69fdc0e93f58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Upper Hand</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bend, OR, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b57fe7a9db67650</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e10120912180ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Data &amp; AI Platform Engineer</t>
+          <t>VIE - Software Engineer (based in Miami)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50ebd00f72efef21</t>
+          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Applied AI Infrastructure Engineer - NREC</t>
+          <t>Senior Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Docker, AKS, CI/CD, Jenkins, Git, Python, R, Optimization</t>
+          <t>RAG, S3, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f3944be5390d23</t>
+          <t>https://www.indeed.com/viewjob?jk=c47699d99f441ed0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c27d39498fc808</t>
+          <t>https://www.indeed.com/viewjob?jk=17379954ea75c1b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AI Systems Engineer - DevOps&amp; Observability - Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Git, Redshift, PostgreSQL, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, MLflow, AKS, CI/CD, GitHub Actions, Git, Kafka, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0c1fe41cb6ffbf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ai Development Specialist</t>
+          <t>Product Engineer I - ArcGIS for Python</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,252 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4bfc6dc3f97709</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Technical Customer Support Engineer, AI Infrastructure &amp; Observability - EMEA</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>clickhouse</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Kinesis, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf74bbdaa26d105</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Lions Path Consulting</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Franklin, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01033f717bc9cb90</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Fintech</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=055e12468c2b025b</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ead9aa90b5f88</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Systems &amp; Network Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Docker, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37d8c5222063ca0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AQR</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Greenwich, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, PyTorch, S3, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfb20f3e398d595</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Mitti Cafe</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23ae46ccdee20ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=b85349be26878a92</t>
         </is>
       </c>
     </row>
